--- a/data/LCIs/Lai_2025/Li_LCIs_BW_Final_v1.xlsx
+++ b/data/LCIs/Lai_2025/Li_LCIs_BW_Final_v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://brgm365.sharepoint.com/sites/RPPEXIMPMET/Documents partages/General/P2/04_Data/04_Modelling/02_LCI modelling/Li_Lithium/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/fasc_metal_sustainability/data/LCIs/Lai_2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="241" documentId="8_{255C1BCC-A7B9-48A3-AB09-6B2D5560E7BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9466FB24-4EC1-4A77-A8B6-33FCBAEFC1A3}"/>
+  <xr:revisionPtr revIDLastSave="261" documentId="8_{255C1BCC-A7B9-48A3-AB09-6B2D5560E7BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3030921-48B4-4B27-90D5-208B78B0A7BD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="885" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Note" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2674" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2687" uniqueCount="223">
   <si>
     <t>Activity</t>
   </si>
@@ -571,9 +571,6 @@
   </si>
   <si>
     <t>Spodumene ore mining in Australia/Greenbushes and Li2CO3 production in China/Shehong</t>
-  </si>
-  <si>
-    <t>AU-CN</t>
   </si>
   <si>
     <t>Spodumene ore mining in Australia/Greenbushes and Li2CO3 production in China/Shehong (Li content)</t>
@@ -2205,6 +2202,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
@@ -2481,12 +2482,12 @@
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="21" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C2" s="22"/>
       <c r="D2" s="22"/>
@@ -3029,10 +3030,10 @@
     <row r="32" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="C33" s="11" t="s">
         <v>210</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>211</v>
       </c>
       <c r="D33" s="12"/>
       <c r="E33" s="12"/>
@@ -3044,10 +3045,10 @@
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D34" s="17"/>
       <c r="E34" s="17"/>
@@ -3059,7 +3060,7 @@
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>123</v>
@@ -3074,7 +3075,7 @@
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>141</v>
@@ -3089,7 +3090,7 @@
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>146</v>
@@ -3104,7 +3105,7 @@
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>175</v>
@@ -3119,10 +3120,10 @@
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D39" s="17"/>
       <c r="E39" s="17"/>
@@ -3134,10 +3135,10 @@
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D40" s="17"/>
       <c r="E40" s="17"/>
@@ -3149,7 +3150,7 @@
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>74</v>
@@ -3164,7 +3165,7 @@
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>93</v>
@@ -3179,7 +3180,7 @@
     </row>
     <row r="43" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="14" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>105</v>
@@ -7331,9 +7332,8 @@
         <f>PR4_Li2CO3_AU_CN_She_Spodumene!B54</f>
         <v>Battery-grade Li2CO3</v>
       </c>
-      <c r="C15" s="1" t="str">
-        <f>PR4_Li2CO3_AU_CN_She_Spodumene!C54</f>
-        <v>AU-CN</v>
+      <c r="C15" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="D15" s="1">
         <v>0.20718982481138803</v>
@@ -7359,9 +7359,8 @@
         <f>PR5_LiOH_AU_CN_She_Spodumene!B28</f>
         <v>Battery-grade LiOH.H2O</v>
       </c>
-      <c r="C16" s="1" t="str">
-        <f>PR5_LiOH_AU_CN_She_Spodumene!C28</f>
-        <v>AU-CN</v>
+      <c r="C16" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="D16" s="1">
         <v>5.919709280325372E-2</v>
@@ -7387,9 +7386,8 @@
         <f>PR6_Li2CO3_CN_Zha!B62</f>
         <v>Battery-grade Li2CO3</v>
       </c>
-      <c r="C17" s="1" t="str">
-        <f>PR6_Li2CO3_CN_Zha!C62</f>
-        <v>AU-CN</v>
+      <c r="C17" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="D17" s="1">
         <v>0.22015447736747248</v>
@@ -7709,9 +7707,8 @@
         <f>+PR4_Li2CO3_AU_CN_She_Spodumene!B66</f>
         <v>Battery-grade Li2CO3 (Li content)</v>
       </c>
-      <c r="C34" s="1" t="str">
-        <f>+PR4_Li2CO3_AU_CN_She_Spodumene!C66</f>
-        <v>AU-CN</v>
+      <c r="C34" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="D34" s="1">
         <v>0.20718982481138803</v>
@@ -7737,9 +7734,8 @@
         <f>+PR5_LiOH_AU_CN_She_Spodumene!B40</f>
         <v>Battery-grade LiOH.H2O (Li content)</v>
       </c>
-      <c r="C35" s="1" t="str">
-        <f>+PR5_LiOH_AU_CN_She_Spodumene!C40</f>
-        <v>AU-CN</v>
+      <c r="C35" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="D35" s="1">
         <v>5.919709280325372E-2</v>
@@ -7765,9 +7761,8 @@
         <f>+PR6_Li2CO3_CN_Zha!B74</f>
         <v>Battery-grade Li2CO3 (Li content)</v>
       </c>
-      <c r="C36" s="1" t="str">
-        <f>+PR6_Li2CO3_CN_Zha!C74</f>
-        <v>AU-CN</v>
+      <c r="C36" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="D36" s="1">
         <v>0.22015447736747248</v>
@@ -7793,9 +7788,8 @@
         <f>PR7_Li2CO3_AR_Olaroz_Brines!B97</f>
         <v>Battery-grade Li2CO3 (Li content)</v>
       </c>
-      <c r="C37" s="1" t="str">
-        <f>PR7_Li2CO3_AR_Olaroz_Brines!C97</f>
-        <v>AR</v>
+      <c r="C37" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="D37" s="1">
         <v>4.2921343914152414E-2</v>
@@ -9057,7 +9051,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -11408,7 +11402,7 @@
         <v>6</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
@@ -11740,7 +11734,7 @@
         <v>2</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>176</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -11825,9 +11819,8 @@
         <f>B47</f>
         <v>Battery-grade Li2CO3</v>
       </c>
-      <c r="C54" s="1" t="str">
-        <f>B48</f>
-        <v>AU-CN</v>
+      <c r="C54" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="D54" s="1">
         <v>1</v>
@@ -11905,7 +11898,7 @@
         <v>0</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
@@ -11921,7 +11914,7 @@
         <v>2</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>176</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
@@ -12006,9 +11999,8 @@
         <f>B59</f>
         <v>Battery-grade Li2CO3 (Li content)</v>
       </c>
-      <c r="C66" s="1" t="str">
-        <f>B60</f>
-        <v>AU-CN</v>
+      <c r="C66" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="D66" s="1">
         <v>1</v>
@@ -12117,7 +12109,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -12157,7 +12149,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -12473,7 +12465,7 @@
         <v>0</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -12489,7 +12481,7 @@
         <v>2</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>176</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -12574,9 +12566,8 @@
         <f>B21</f>
         <v>Battery-grade LiOH.H2O</v>
       </c>
-      <c r="C28" s="1" t="str">
-        <f>B22</f>
-        <v>AU-CN</v>
+      <c r="C28" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="D28" s="1">
         <v>1</v>
@@ -12654,7 +12645,7 @@
         <v>0</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
@@ -12670,7 +12661,7 @@
         <v>2</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>176</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
@@ -12755,9 +12746,8 @@
         <f>B33</f>
         <v>Battery-grade LiOH.H2O (Li content)</v>
       </c>
-      <c r="C40" s="1" t="str">
-        <f>B34</f>
-        <v>AU-CN</v>
+      <c r="C40" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="D40" s="1">
         <v>1</v>
@@ -12865,7 +12855,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -12905,7 +12895,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -13007,7 +12997,7 @@
         <v>23</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -13033,7 +13023,7 @@
         <v>23</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -13059,7 +13049,7 @@
         <v>23</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -13085,7 +13075,7 @@
         <v>23</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -13111,7 +13101,7 @@
         <v>23</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -13137,15 +13127,15 @@
         <v>23</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>184</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>79</v>
@@ -13163,15 +13153,15 @@
         <v>23</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>184</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>79</v>
@@ -13189,15 +13179,15 @@
         <v>23</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>184</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>79</v>
@@ -13215,15 +13205,15 @@
         <v>23</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>184</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>79</v>
@@ -13241,15 +13231,15 @@
         <v>23</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>186</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>25</v>
@@ -13267,15 +13257,15 @@
         <v>23</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>186</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>25</v>
@@ -13293,7 +13283,7 @@
         <v>23</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -13319,7 +13309,7 @@
         <v>23</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -13345,7 +13335,7 @@
         <v>23</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -13371,15 +13361,15 @@
         <v>23</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>20</v>
@@ -13397,7 +13387,7 @@
         <v>23</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -13423,15 +13413,15 @@
         <v>23</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>190</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>25</v>
@@ -13449,15 +13439,15 @@
         <v>23</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>192</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>25</v>
@@ -13475,15 +13465,15 @@
         <v>23</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>194</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>20</v>
@@ -13501,15 +13491,15 @@
         <v>23</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>25</v>
@@ -13527,15 +13517,15 @@
         <v>23</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>25</v>
@@ -13553,7 +13543,7 @@
         <v>23</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -13579,7 +13569,7 @@
         <v>23</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -13605,7 +13595,7 @@
         <v>23</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -13631,7 +13621,7 @@
         <v>23</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -13657,7 +13647,7 @@
         <v>23</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -13680,7 +13670,7 @@
         <v>30</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -13703,7 +13693,7 @@
         <v>30</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -13726,12 +13716,12 @@
         <v>30</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D39" s="1">
         <v>5.0000000000000002E-5</v>
@@ -13749,12 +13739,12 @@
         <v>32</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D40" s="1">
         <v>7.0000000000000007E-5</v>
@@ -13772,12 +13762,12 @@
         <v>32</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D41" s="1">
         <v>2.0000000000000002E-5</v>
@@ -13795,12 +13785,12 @@
         <v>32</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D42" s="1">
         <v>9.8999999999999999E-4</v>
@@ -13818,12 +13808,12 @@
         <v>32</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D43" s="1">
         <v>3.2000000000000003E-4</v>
@@ -13841,7 +13831,7 @@
         <v>32</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -13864,12 +13854,12 @@
         <v>32</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D45" s="1">
         <v>0.28999999999999998</v>
@@ -13887,12 +13877,12 @@
         <v>31</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D46" s="1">
         <v>7.0000000000000007E-2</v>
@@ -13910,12 +13900,12 @@
         <v>31</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D47" s="1">
         <v>0.19</v>
@@ -13933,12 +13923,12 @@
         <v>31</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D48" s="1">
         <v>0.39</v>
@@ -13956,12 +13946,12 @@
         <v>31</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D49" s="1">
         <v>0.09</v>
@@ -13979,12 +13969,12 @@
         <v>31</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D50" s="1">
         <v>0.26</v>
@@ -14002,12 +13992,12 @@
         <v>31</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D51" s="1">
         <v>0.03</v>
@@ -14025,12 +14015,12 @@
         <v>31</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D52" s="1">
         <v>3.0000000000000001E-3</v>
@@ -14048,7 +14038,7 @@
         <v>31</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="53" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -14057,7 +14047,7 @@
         <v>0</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
@@ -14073,7 +14063,7 @@
         <v>2</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>176</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
@@ -14158,9 +14148,8 @@
         <f>B55</f>
         <v>Battery-grade Li2CO3</v>
       </c>
-      <c r="C62" s="1" t="str">
-        <f>B56</f>
-        <v>AU-CN</v>
+      <c r="C62" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="D62" s="1">
         <v>1</v>
@@ -14238,7 +14227,7 @@
         <v>0</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
@@ -14254,7 +14243,7 @@
         <v>2</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>176</v>
+        <v>79</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
@@ -14339,9 +14328,8 @@
         <f>B67</f>
         <v>Battery-grade Li2CO3 (Li content)</v>
       </c>
-      <c r="C74" s="1" t="str">
-        <f>B68</f>
-        <v>AU-CN</v>
+      <c r="C74" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="D74" s="1">
         <v>1</v>
@@ -16759,6 +16747,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d78c010b-218d-4be4-b2d9-423b1f51aae5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="adc0c41a-12c1-4165-8422-5f5ca88e9f6a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004741122952C13D46BBBC92EEAE11CF32" ma:contentTypeVersion="13" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="d96b5fa62e5213e7d24e66b2bac0c378">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d78c010b-218d-4be4-b2d9-423b1f51aae5" xmlns:ns3="adc0c41a-12c1-4165-8422-5f5ca88e9f6a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c2e8fc9a9c70fab2c0f7259df75af726" ns2:_="" ns3:_="">
     <xsd:import namespace="d78c010b-218d-4be4-b2d9-423b1f51aae5"/>
@@ -16981,27 +16989,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d78c010b-218d-4be4-b2d9-423b1f51aae5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="adc0c41a-12c1-4165-8422-5f5ca88e9f6a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C49650B-771C-479B-A626-56D20740AF7D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d78c010b-218d-4be4-b2d9-423b1f51aae5"/>
+    <ds:schemaRef ds:uri="adc0c41a-12c1-4165-8422-5f5ca88e9f6a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{384B8E01-8C38-4B5E-84E8-911B9D561447}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4D1F781-2DAC-4C03-B127-AE9F76DA19C9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17018,23 +17025,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C49650B-771C-479B-A626-56D20740AF7D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d78c010b-218d-4be4-b2d9-423b1f51aae5"/>
-    <ds:schemaRef ds:uri="adc0c41a-12c1-4165-8422-5f5ca88e9f6a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{384B8E01-8C38-4B5E-84E8-911B9D561447}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/LCIs/Lai_2025/Li_LCIs_BW_Final_v1.xlsx
+++ b/data/LCIs/Lai_2025/Li_LCIs_BW_Final_v1.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="261" documentId="8_{255C1BCC-A7B9-48A3-AB09-6B2D5560E7BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3030921-48B4-4B27-90D5-208B78B0A7BD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="885" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="885" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Note" sheetId="1" r:id="rId1"/>
@@ -16747,26 +16747,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d78c010b-218d-4be4-b2d9-423b1f51aae5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="adc0c41a-12c1-4165-8422-5f5ca88e9f6a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004741122952C13D46BBBC92EEAE11CF32" ma:contentTypeVersion="13" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="d96b5fa62e5213e7d24e66b2bac0c378">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d78c010b-218d-4be4-b2d9-423b1f51aae5" xmlns:ns3="adc0c41a-12c1-4165-8422-5f5ca88e9f6a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c2e8fc9a9c70fab2c0f7259df75af726" ns2:_="" ns3:_="">
     <xsd:import namespace="d78c010b-218d-4be4-b2d9-423b1f51aae5"/>
@@ -16989,26 +16969,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C49650B-771C-479B-A626-56D20740AF7D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d78c010b-218d-4be4-b2d9-423b1f51aae5"/>
-    <ds:schemaRef ds:uri="adc0c41a-12c1-4165-8422-5f5ca88e9f6a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{384B8E01-8C38-4B5E-84E8-911B9D561447}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d78c010b-218d-4be4-b2d9-423b1f51aae5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="adc0c41a-12c1-4165-8422-5f5ca88e9f6a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4D1F781-2DAC-4C03-B127-AE9F76DA19C9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17025,4 +17006,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{384B8E01-8C38-4B5E-84E8-911B9D561447}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C49650B-771C-479B-A626-56D20740AF7D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d78c010b-218d-4be4-b2d9-423b1f51aae5"/>
+    <ds:schemaRef ds:uri="adc0c41a-12c1-4165-8422-5f5ca88e9f6a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>